--- a/data/trans_dic/P1409-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1409-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,96</t>
+          <t>0,63; 3,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,8</t>
+          <t>0,78; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,51</t>
+          <t>2,01; 5,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,27</t>
+          <t>0,36; 3,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,91</t>
+          <t>1,31; 4,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,33</t>
+          <t>3,11; 6,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,77</t>
+          <t>0,77; 2,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,62</t>
+          <t>1,38; 3,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,25</t>
+          <t>2,86; 5,13</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,38</t>
+          <t>0,5; 3,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,79</t>
+          <t>1,21; 4,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 8,31</t>
+          <t>2,6; 6,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,16</t>
+          <t>2,05; 7,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,2</t>
+          <t>2,71; 7,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,46</t>
+          <t>4,59; 8,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,23</t>
+          <t>1,65; 4,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,97</t>
+          <t>2,23; 5,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,3</t>
+          <t>3,85; 6,87</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,93</t>
+          <t>0,93; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,35</t>
+          <t>0,84; 3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,59</t>
+          <t>1,47; 4,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,84</t>
+          <t>1,15; 5,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,02</t>
+          <t>0,66; 7,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,62</t>
+          <t>2,27; 6,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,23</t>
+          <t>1,28; 3,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,36</t>
+          <t>1,08; 3,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,75</t>
+          <t>1,9; 4,67</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,04</t>
+          <t>1,25; 3,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,12</t>
+          <t>1,38; 3,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,11</t>
+          <t>2,63; 5,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,18</t>
+          <t>1,65; 4,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,59</t>
+          <t>2,14; 4,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,01</t>
+          <t>3,47; 5,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,99</t>
+          <t>1,74; 3,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,35</t>
+          <t>1,91; 3,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,51</t>
+          <t>3,31; 5,04</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,99</t>
+          <t>1,06; 3,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,18</t>
+          <t>2,27; 5,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,61</t>
+          <t>3,51; 8,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,58</t>
+          <t>1,94; 4,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,4</t>
+          <t>3,71; 7,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 35,45</t>
+          <t>3,87; 6,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,73</t>
+          <t>1,93; 3,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,77</t>
+          <t>3,46; 5,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 30,95</t>
+          <t>4,21; 6,43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,01</t>
+          <t>1,04; 5,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,5</t>
+          <t>2,46; 7,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 11,25</t>
+          <t>0,23; 11,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,39</t>
+          <t>1,65; 3,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,41</t>
+          <t>2,8; 5,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,89</t>
+          <t>3,14; 5,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,46</t>
+          <t>1,76; 3,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,39</t>
+          <t>3,05; 5,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,19</t>
+          <t>3,03; 5,85</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,44</t>
+          <t>1,46; 2,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,11</t>
+          <t>2,04; 3,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,61</t>
+          <t>3,1; 4,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,36</t>
+          <t>2,18; 3,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,62</t>
+          <t>3,24; 4,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 14,12</t>
+          <t>4,2; 5,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,73</t>
+          <t>1,98; 2,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,69</t>
+          <t>2,79; 3,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,89</t>
+          <t>3,85; 4,82</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37435</t>
+          <t>40604</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2892; 12928</t>
+          <t>2744; 13228</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3795; 16285</t>
+          <t>3335; 17297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9831; 27851</t>
+          <t>11063; 30608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1883; 13420</t>
+          <t>1137; 11909</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4984; 17027</t>
+          <t>4549; 16831</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13532; 28322</t>
+          <t>15185; 30163</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5987; 20818</t>
+          <t>5820; 20802</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10363; 28094</t>
+          <t>10733; 27924</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28079; 50011</t>
+          <t>29762; 53334</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23749</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43253</t>
+          <t>47239</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2071; 14165</t>
+          <t>2106; 15648</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4645; 18084</t>
+          <t>4575; 18675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11005; 37589</t>
+          <t>12584; 32457</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7129; 24203</t>
+          <t>6931; 23662</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10658; 26805</t>
+          <t>10093; 26743</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17127; 32327</t>
+          <t>19405; 36565</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12514; 32047</t>
+          <t>12509; 33071</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17107; 37284</t>
+          <t>16728; 37685</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32920; 60881</t>
+          <t>34893; 62216</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>20807</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5571; 18466</t>
+          <t>5845; 18855</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4301; 17493</t>
+          <t>4372; 17509</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2869; 23981</t>
+          <t>6909; 23202</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3002; 15204</t>
+          <t>2985; 14905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1623; 11669</t>
+          <t>1090; 12442</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3932; 11053</t>
+          <t>4252; 12372</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11021; 28723</t>
+          <t>11385; 28217</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7575; 23104</t>
+          <t>7407; 23117</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6405; 31295</t>
+          <t>12515; 30754</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37514</t>
+          <t>42298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>39332</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72091</t>
+          <t>81630</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14874; 35280</t>
+          <t>14504; 35286</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15500; 35817</t>
+          <t>15836; 34943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25964; 52850</t>
+          <t>29822; 59433</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12635; 31931</t>
+          <t>12642; 31447</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17584; 37881</t>
+          <t>17660; 37220</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17663; 49016</t>
+          <t>29901; 50197</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31291; 57464</t>
+          <t>33388; 59413</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37037; 66109</t>
+          <t>37728; 64686</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48617; 90711</t>
+          <t>65901; 100415</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>106127</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>135239</t>
+          <t>71874</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5858; 20373</t>
+          <t>5394; 18607</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13701; 32128</t>
+          <t>14097; 31758</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18713; 45439</t>
+          <t>19838; 46141</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14796; 34798</t>
+          <t>14766; 34445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28225; 54660</t>
+          <t>27392; 53312</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36449; 297050</t>
+          <t>32047; 51635</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24207; 47432</t>
+          <t>24564; 49860</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46729; 78412</t>
+          <t>47079; 77262</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>64858; 405559</t>
+          <t>58659; 89700</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>35735</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>42560</t>
+          <t>44231</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2909; 13384</t>
+          <t>2775; 13344</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7296; 21541</t>
+          <t>7076; 21621</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>537; 27050</t>
+          <t>538; 26385</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17569; 37552</t>
+          <t>18339; 38143</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30371; 58505</t>
+          <t>30329; 57629</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25062; 44732</t>
+          <t>26463; 46910</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23787; 47596</t>
+          <t>24149; 47407</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>41657; 73797</t>
+          <t>41822; 73898</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31145; 61871</t>
+          <t>32679; 63218</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124068</t>
+          <t>132956</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>225128</t>
+          <t>173427</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>349196</t>
+          <t>306384</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50078; 83475</t>
+          <t>49846; 82842</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>68218; 105187</t>
+          <t>69218; 104873</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92206; 155587</t>
+          <t>106542; 160450</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76722; 119016</t>
+          <t>77443; 115660</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>118189; 163273</t>
+          <t>114267; 163570</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>150125; 504164</t>
+          <t>152427; 194990</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>140092; 190117</t>
+          <t>138298; 188678</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>195314; 255319</t>
+          <t>193331; 256047</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>268324; 617581</t>
+          <t>271974; 340557</t>
         </is>
       </c>
     </row>
